--- a/Company Yearly Sales.xlsx
+++ b/Company Yearly Sales.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="153222"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="127">
   <si>
     <t>Region</t>
   </si>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>Sum of Total Cost</t>
-  </si>
-  <si>
-    <t>Count of Item Type</t>
   </si>
   <si>
     <t>Max of Ship Days</t>
@@ -1020,7 +1017,76 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="55">
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
@@ -1053,54 +1119,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -1136,6 +1154,30 @@
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color theme="1"/>
@@ -1164,8 +1206,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="SlicerStyleLight1 2" pivot="0" table="0" count="10">
-      <tableStyleElement type="wholeTable" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="wholeTable" dxfId="54"/>
+      <tableStyleElement type="headerRow" dxfId="53"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1760,9 +1802,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -1844,9 +1884,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -1928,9 +1966,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2012,9 +2048,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2096,9 +2130,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2180,9 +2212,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2264,9 +2294,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2418,9 +2446,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2438,9 +2464,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2458,9 +2482,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2478,9 +2500,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2498,9 +2518,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2518,9 +2536,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2538,9 +2554,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -2676,12 +2690,12 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:shape val="box"/>
-        <c:axId val="229727352"/>
-        <c:axId val="229726568"/>
+        <c:axId val="287322456"/>
+        <c:axId val="287322848"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="229727352"/>
+        <c:axId val="287322456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,7 +2737,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="229726568"/>
+        <c:crossAx val="287322848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2731,7 +2745,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="229726568"/>
+        <c:axId val="287322848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2741,7 +2755,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="229727352"/>
+        <c:crossAx val="287322456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3840,11 +3854,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="50"/>
-        <c:axId val="229728136"/>
-        <c:axId val="229728920"/>
+        <c:axId val="287324024"/>
+        <c:axId val="287325984"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="229728136"/>
+        <c:axId val="287324024"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3887,7 +3901,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="229728920"/>
+        <c:crossAx val="287325984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3895,7 +3909,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="229728920"/>
+        <c:axId val="287325984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3932,7 +3946,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="229728136"/>
+        <c:crossAx val="287324024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4539,9 +4553,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -4612,9 +4624,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -4774,9 +4784,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -4821,9 +4829,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -5137,7 +5143,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -5175,9 +5180,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -5269,7 +5272,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -5389,11 +5391,11 @@
         </c:dLbls>
         <c:gapWidth val="65"/>
         <c:overlap val="-20"/>
-        <c:axId val="292955416"/>
-        <c:axId val="292956592"/>
+        <c:axId val="287320104"/>
+        <c:axId val="287777872"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="292955416"/>
+        <c:axId val="287320104"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -5436,7 +5438,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="292956592"/>
+        <c:crossAx val="287777872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5444,7 +5446,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="292956592"/>
+        <c:axId val="287777872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5454,7 +5456,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="292955416"/>
+        <c:crossAx val="287320104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5967,11 +5969,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="292957376"/>
-        <c:axId val="292960120"/>
+        <c:axId val="287773952"/>
+        <c:axId val="287770816"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="292957376"/>
+        <c:axId val="287773952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6014,7 +6016,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="292960120"/>
+        <c:crossAx val="287770816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6022,7 +6024,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="292960120"/>
+        <c:axId val="287770816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6059,7 +6061,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="292957376"/>
+        <c:crossAx val="287773952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14542,550 +14544,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
-  <location ref="A33:B40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="102">
-        <item x="60"/>
-        <item x="7"/>
-        <item x="91"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="5"/>
-        <item x="96"/>
-        <item x="25"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="77"/>
-        <item x="95"/>
-        <item x="83"/>
-        <item x="55"/>
-        <item x="22"/>
-        <item x="90"/>
-        <item x="94"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="63"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="61"/>
-        <item x="40"/>
-        <item x="15"/>
-        <item x="71"/>
-        <item x="99"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="59"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="58"/>
-        <item x="33"/>
-        <item x="46"/>
-        <item x="54"/>
-        <item x="3"/>
-        <item x="29"/>
-        <item x="93"/>
-        <item x="19"/>
-        <item x="24"/>
-        <item x="45"/>
-        <item x="26"/>
-        <item x="84"/>
-        <item x="36"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="87"/>
-        <item x="89"/>
-        <item x="17"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="32"/>
-        <item x="72"/>
-        <item x="8"/>
-        <item x="28"/>
-        <item x="57"/>
-        <item x="21"/>
-        <item x="88"/>
-        <item x="65"/>
-        <item x="80"/>
-        <item x="48"/>
-        <item x="97"/>
-        <item x="92"/>
-        <item x="30"/>
-        <item x="66"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="50"/>
-        <item x="35"/>
-        <item x="79"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="67"/>
-        <item x="74"/>
-        <item x="98"/>
-        <item x="44"/>
-        <item x="39"/>
-        <item x="78"/>
-        <item x="70"/>
-        <item x="76"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="82"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="75"/>
-        <item x="2"/>
-        <item x="27"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="8">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="5">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
-  <location ref="H3:H4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="15">
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="102">
-        <item x="60"/>
-        <item x="7"/>
-        <item x="91"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="5"/>
-        <item x="96"/>
-        <item x="25"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="77"/>
-        <item x="95"/>
-        <item x="83"/>
-        <item x="55"/>
-        <item x="22"/>
-        <item x="90"/>
-        <item x="94"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="63"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="61"/>
-        <item x="40"/>
-        <item x="15"/>
-        <item x="71"/>
-        <item x="99"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="59"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="58"/>
-        <item x="33"/>
-        <item x="46"/>
-        <item x="54"/>
-        <item x="3"/>
-        <item x="29"/>
-        <item x="93"/>
-        <item x="19"/>
-        <item x="24"/>
-        <item x="45"/>
-        <item x="26"/>
-        <item x="84"/>
-        <item x="36"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="87"/>
-        <item x="89"/>
-        <item x="17"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="32"/>
-        <item x="72"/>
-        <item x="8"/>
-        <item x="28"/>
-        <item x="57"/>
-        <item x="21"/>
-        <item x="88"/>
-        <item x="65"/>
-        <item x="80"/>
-        <item x="48"/>
-        <item x="97"/>
-        <item x="92"/>
-        <item x="30"/>
-        <item x="66"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="50"/>
-        <item x="35"/>
-        <item x="79"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="67"/>
-        <item x="74"/>
-        <item x="98"/>
-        <item x="44"/>
-        <item x="39"/>
-        <item x="78"/>
-        <item x="70"/>
-        <item x="76"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="82"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="75"/>
-        <item x="2"/>
-        <item x="27"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="102">
-        <item x="99"/>
-        <item x="98"/>
-        <item x="95"/>
-        <item x="97"/>
-        <item x="96"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="92"/>
-        <item x="91"/>
-        <item x="90"/>
-        <item x="89"/>
-        <item x="88"/>
-        <item x="87"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="71"/>
-        <item x="86"/>
-        <item x="78"/>
-        <item x="82"/>
-        <item x="76"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="60"/>
-        <item x="79"/>
-        <item x="77"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="52"/>
-        <item x="69"/>
-        <item x="72"/>
-        <item x="70"/>
-        <item x="68"/>
-        <item x="59"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="48"/>
-        <item x="67"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="61"/>
-        <item x="55"/>
-        <item x="54"/>
-        <item x="42"/>
-        <item x="75"/>
-        <item x="56"/>
-        <item x="39"/>
-        <item x="37"/>
-        <item x="58"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="47"/>
-        <item x="31"/>
-        <item x="63"/>
-        <item x="45"/>
-        <item x="30"/>
-        <item x="29"/>
-        <item x="27"/>
-        <item x="40"/>
-        <item x="20"/>
-        <item x="41"/>
-        <item x="57"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="33"/>
-        <item x="53"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="43"/>
-        <item x="18"/>
-        <item x="21"/>
-        <item x="44"/>
-        <item x="17"/>
-        <item x="51"/>
-        <item x="16"/>
-        <item x="38"/>
-        <item x="46"/>
-        <item x="13"/>
-        <item x="25"/>
-        <item x="34"/>
-        <item x="23"/>
-        <item x="11"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="26"/>
-        <item x="24"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
   <location ref="D38:E39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -15246,10 +14704,10 @@
     <dataField name="Sum of Total Cost" fld="13" baseField="4" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="24">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -15262,9 +14720,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54" rowHeaderCaption="Sales Channel">
-  <location ref="D17:E19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54" rowHeaderCaption="Sales Channel">
+  <location ref="K19:K20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField showAll="0">
       <items count="9">
@@ -15281,7 +14739,7 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
+    <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="1"/>
@@ -15405,7 +14863,112 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="102">
+        <item x="52"/>
+        <item x="24"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="97"/>
+        <item x="44"/>
+        <item x="94"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="68"/>
+        <item x="27"/>
+        <item x="34"/>
+        <item x="19"/>
+        <item x="66"/>
+        <item x="39"/>
+        <item x="58"/>
+        <item x="0"/>
+        <item x="65"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="57"/>
+        <item x="82"/>
+        <item x="92"/>
+        <item x="7"/>
+        <item x="60"/>
+        <item x="85"/>
+        <item x="9"/>
+        <item x="53"/>
+        <item x="61"/>
+        <item x="80"/>
+        <item x="25"/>
+        <item x="38"/>
+        <item x="84"/>
+        <item x="62"/>
+        <item x="26"/>
+        <item x="32"/>
+        <item x="49"/>
+        <item x="89"/>
+        <item x="83"/>
+        <item x="99"/>
+        <item x="88"/>
+        <item x="79"/>
+        <item x="4"/>
+        <item x="50"/>
+        <item x="18"/>
+        <item x="67"/>
+        <item x="36"/>
+        <item x="77"/>
+        <item x="31"/>
+        <item x="28"/>
+        <item x="96"/>
+        <item x="75"/>
+        <item x="20"/>
+        <item x="5"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="91"/>
+        <item x="16"/>
+        <item x="81"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="76"/>
+        <item x="70"/>
+        <item x="41"/>
+        <item x="93"/>
+        <item x="64"/>
+        <item x="30"/>
+        <item x="55"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="90"/>
+        <item x="95"/>
+        <item x="98"/>
+        <item x="21"/>
+        <item x="51"/>
+        <item x="40"/>
+        <item x="72"/>
+        <item x="63"/>
+        <item x="45"/>
+        <item x="74"/>
+        <item x="35"/>
+        <item x="33"/>
+        <item x="43"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="87"/>
+        <item x="48"/>
+        <item x="86"/>
+        <item x="69"/>
+        <item x="54"/>
+        <item x="71"/>
+        <item x="10"/>
+        <item x="59"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -15415,124 +14978,15 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="1">
+    <i/>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Orders" fld="3" subtotal="count" baseField="3" baseItem="0"/>
+    <dataField name="Count of Order ID" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="50" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="50" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="50" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="52" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="52" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="52" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -15542,7 +14996,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Item Type">
   <location ref="D23:E24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -15720,7 +15174,7 @@
     <dataField name="Average of Unit Price" fld="10" subtotal="average" baseField="2" baseItem="8" numFmtId="166"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="25">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15733,7 +15187,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="48" rowHeaderCaption="Item Type">
   <location ref="G17:H29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -16049,7 +15503,7 @@
     <dataField name="Sum of Total Profit" fld="14" baseField="2" baseItem="2"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="26">
+    <format dxfId="48">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16091,9 +15545,503 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order ID">
+  <location ref="K3:L4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" sortType="descending">
+      <items count="14">
+        <item h="1" x="3"/>
+        <item x="10"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="0"/>
+        <item h="1" x="11"/>
+        <item h="1" x="1"/>
+        <item h="1" x="8"/>
+        <item h="1" x="2"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="12"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="102">
+        <item x="60"/>
+        <item x="7"/>
+        <item x="91"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="96"/>
+        <item x="25"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="77"/>
+        <item x="95"/>
+        <item x="83"/>
+        <item x="55"/>
+        <item x="22"/>
+        <item x="90"/>
+        <item x="94"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="63"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="61"/>
+        <item x="40"/>
+        <item x="15"/>
+        <item x="71"/>
+        <item x="99"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="58"/>
+        <item x="33"/>
+        <item x="46"/>
+        <item x="54"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="93"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="45"/>
+        <item x="26"/>
+        <item x="84"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="87"/>
+        <item x="89"/>
+        <item x="17"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="32"/>
+        <item x="72"/>
+        <item x="8"/>
+        <item x="28"/>
+        <item x="57"/>
+        <item x="21"/>
+        <item x="88"/>
+        <item x="65"/>
+        <item x="80"/>
+        <item x="48"/>
+        <item x="97"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="66"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="50"/>
+        <item x="35"/>
+        <item x="79"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="67"/>
+        <item x="74"/>
+        <item x="98"/>
+        <item x="44"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="70"/>
+        <item x="76"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="82"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="75"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="102">
+        <item h="1" x="52"/>
+        <item h="1" x="24"/>
+        <item h="1" x="56"/>
+        <item h="1" x="23"/>
+        <item h="1" x="97"/>
+        <item h="1" x="44"/>
+        <item h="1" x="94"/>
+        <item h="1" x="12"/>
+        <item h="1" x="22"/>
+        <item h="1" x="6"/>
+        <item h="1" x="68"/>
+        <item h="1" x="27"/>
+        <item h="1" x="34"/>
+        <item h="1" x="19"/>
+        <item h="1" x="66"/>
+        <item h="1" x="39"/>
+        <item h="1" x="58"/>
+        <item h="1" x="0"/>
+        <item h="1" x="65"/>
+        <item h="1" x="3"/>
+        <item h="1" x="8"/>
+        <item h="1" x="11"/>
+        <item h="1" x="15"/>
+        <item h="1" x="46"/>
+        <item h="1" x="2"/>
+        <item h="1" x="57"/>
+        <item h="1" x="82"/>
+        <item h="1" x="92"/>
+        <item h="1" x="7"/>
+        <item h="1" x="60"/>
+        <item h="1" x="85"/>
+        <item h="1" x="9"/>
+        <item h="1" x="53"/>
+        <item h="1" x="61"/>
+        <item h="1" x="80"/>
+        <item h="1" x="25"/>
+        <item h="1" x="38"/>
+        <item h="1" x="84"/>
+        <item h="1" x="62"/>
+        <item h="1" x="26"/>
+        <item h="1" x="32"/>
+        <item h="1" x="49"/>
+        <item h="1" x="89"/>
+        <item h="1" x="83"/>
+        <item h="1" x="99"/>
+        <item h="1" x="88"/>
+        <item h="1" x="79"/>
+        <item h="1" x="4"/>
+        <item h="1" x="50"/>
+        <item h="1" x="18"/>
+        <item h="1" x="67"/>
+        <item h="1" x="36"/>
+        <item x="77"/>
+        <item h="1" x="31"/>
+        <item h="1" x="28"/>
+        <item h="1" x="96"/>
+        <item h="1" x="75"/>
+        <item h="1" x="20"/>
+        <item h="1" x="5"/>
+        <item h="1" x="29"/>
+        <item h="1" x="14"/>
+        <item h="1" x="13"/>
+        <item h="1" x="1"/>
+        <item h="1" x="91"/>
+        <item h="1" x="16"/>
+        <item h="1" x="81"/>
+        <item h="1" x="17"/>
+        <item h="1" x="37"/>
+        <item h="1" x="76"/>
+        <item h="1" x="70"/>
+        <item h="1" x="41"/>
+        <item h="1" x="93"/>
+        <item h="1" x="64"/>
+        <item h="1" x="30"/>
+        <item h="1" x="55"/>
+        <item h="1" x="73"/>
+        <item h="1" x="42"/>
+        <item h="1" x="90"/>
+        <item h="1" x="95"/>
+        <item h="1" x="98"/>
+        <item h="1" x="21"/>
+        <item h="1" x="51"/>
+        <item h="1" x="40"/>
+        <item h="1" x="72"/>
+        <item h="1" x="63"/>
+        <item h="1" x="45"/>
+        <item h="1" x="74"/>
+        <item h="1" x="35"/>
+        <item h="1" x="33"/>
+        <item h="1" x="43"/>
+        <item h="1" x="47"/>
+        <item h="1" x="78"/>
+        <item h="1" x="87"/>
+        <item h="1" x="48"/>
+        <item h="1" x="86"/>
+        <item h="1" x="69"/>
+        <item h="1" x="54"/>
+        <item h="1" x="71"/>
+        <item h="1" x="10"/>
+        <item h="1" x="59"/>
+        <item h="1" x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="1">
+    <i>
+      <x v="52"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Ship Days" fld="7" subtotal="max" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Item Type">
+  <location ref="D33:E34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="3"/>
+        <item h="1" x="10"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="0"/>
+        <item h="1" x="11"/>
+        <item h="1" x="1"/>
+        <item h="1" x="8"/>
+        <item h="1" x="2"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="102">
+        <item x="60"/>
+        <item x="7"/>
+        <item x="91"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="96"/>
+        <item x="25"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="77"/>
+        <item x="95"/>
+        <item x="83"/>
+        <item x="55"/>
+        <item x="22"/>
+        <item x="90"/>
+        <item x="94"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="63"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="61"/>
+        <item x="40"/>
+        <item x="15"/>
+        <item x="71"/>
+        <item x="99"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="58"/>
+        <item x="33"/>
+        <item x="46"/>
+        <item x="54"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="93"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="45"/>
+        <item x="26"/>
+        <item x="84"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="87"/>
+        <item x="89"/>
+        <item x="17"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="32"/>
+        <item x="72"/>
+        <item x="8"/>
+        <item x="28"/>
+        <item x="57"/>
+        <item x="21"/>
+        <item x="88"/>
+        <item x="65"/>
+        <item x="80"/>
+        <item x="48"/>
+        <item x="97"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="66"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="50"/>
+        <item x="35"/>
+        <item x="79"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="67"/>
+        <item x="74"/>
+        <item x="98"/>
+        <item x="44"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="70"/>
+        <item x="76"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="82"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="75"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="1">
+    <i>
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Profit" fld="14" baseField="2" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="50">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
-  <location ref="H6:H7" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
+  <location ref="H9:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField showAll="0">
       <items count="9">
@@ -16339,7 +16287,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
+    <pivotField showAll="0">
       <items count="102">
         <item x="99"/>
         <item x="98"/>
@@ -16445,7 +16393,112 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="102">
+        <item x="99"/>
+        <item x="98"/>
+        <item x="97"/>
+        <item x="96"/>
+        <item x="95"/>
+        <item x="94"/>
+        <item x="93"/>
+        <item x="92"/>
+        <item x="91"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="88"/>
+        <item x="87"/>
+        <item x="86"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="83"/>
+        <item x="82"/>
+        <item x="81"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="78"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="75"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="72"/>
+        <item x="71"/>
+        <item x="70"/>
+        <item x="69"/>
+        <item x="68"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="64"/>
+        <item x="63"/>
+        <item x="62"/>
+        <item x="61"/>
+        <item x="60"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="53"/>
+        <item x="52"/>
+        <item x="51"/>
+        <item x="50"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="45"/>
+        <item x="44"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="41"/>
+        <item x="40"/>
+        <item x="39"/>
+        <item x="38"/>
+        <item x="37"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -16454,13 +16507,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Cost" fld="13" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Profit" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="28">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16474,10 +16527,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Region">
-  <location ref="E3:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54" rowHeaderCaption="Sales Channel">
+  <location ref="D17:E19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="9">
         <item x="4"/>
         <item x="1"/>
@@ -16492,7 +16545,14 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="6">
         <item x="2"/>
@@ -16615,118 +16675,29 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="0"/>
+    <field x="3"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="2">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Count of Orders" fld="3" subtotal="count" baseField="3" baseItem="0"/>
   </dataFields>
-  <formats count="9">
-    <format dxfId="37">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="36">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="33">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="29">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="32" format="2" series="1">
+  <chartFormats count="9">
+    <chartFormat chart="50" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -16735,86 +16706,92 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="3">
+    <chartFormat chart="50" format="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="6"/>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="4">
+    <chartFormat chart="50" format="2">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="5">
+    <chartFormat chart="52" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="52" format="4">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="6">
+    <chartFormat chart="52" format="5">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="5"/>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="7">
+    <chartFormat chart="53" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="7">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="32" format="8">
+    <chartFormat chart="53" format="8">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="0" count="1" selected="0">
+          <reference field="3" count="1" selected="0">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="32" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -16830,727 +16807,24 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Item Type">
-  <location ref="K3:L4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Region">
+  <location ref="D28:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
+        <item h="1" x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="6"/>
         <item x="5"/>
         <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="14">
-        <item h="1" x="3"/>
-        <item x="10"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item h="1" x="0"/>
-        <item h="1" x="11"/>
-        <item h="1" x="1"/>
-        <item h="1" x="8"/>
-        <item h="1" x="2"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item h="1" x="6"/>
-        <item h="1" x="12"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="102">
-        <item x="60"/>
-        <item x="7"/>
-        <item x="91"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="5"/>
-        <item x="96"/>
-        <item x="25"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="77"/>
-        <item x="95"/>
-        <item x="83"/>
-        <item x="55"/>
-        <item x="22"/>
-        <item x="90"/>
-        <item x="94"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="63"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="61"/>
-        <item x="40"/>
-        <item x="15"/>
-        <item x="71"/>
-        <item x="99"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="59"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="58"/>
-        <item x="33"/>
-        <item x="46"/>
-        <item x="54"/>
-        <item x="3"/>
-        <item x="29"/>
-        <item x="93"/>
-        <item x="19"/>
-        <item x="24"/>
-        <item x="45"/>
-        <item x="26"/>
-        <item x="84"/>
-        <item x="36"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="87"/>
-        <item x="89"/>
-        <item x="17"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="32"/>
-        <item x="72"/>
-        <item x="8"/>
-        <item x="28"/>
-        <item x="57"/>
-        <item x="21"/>
-        <item x="88"/>
-        <item x="65"/>
-        <item x="80"/>
-        <item x="48"/>
-        <item x="97"/>
-        <item x="92"/>
-        <item x="30"/>
-        <item x="66"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="50"/>
-        <item x="35"/>
-        <item x="79"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="67"/>
-        <item x="74"/>
-        <item x="98"/>
-        <item x="44"/>
-        <item x="39"/>
-        <item x="78"/>
-        <item x="70"/>
-        <item x="76"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="82"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="75"/>
-        <item x="2"/>
-        <item x="27"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="1">
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Ship Days" fld="7" subtotal="max" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="88" rowHeaderCaption="Country">
-  <location ref="A3:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="78">
-        <item h="1" x="51"/>
-        <item h="1" x="22"/>
-        <item h="1" x="38"/>
-        <item h="1" x="32"/>
-        <item x="7"/>
-        <item h="1" x="24"/>
-        <item h="1" x="37"/>
-        <item h="1" x="15"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="21"/>
-        <item h="1" x="42"/>
-        <item h="1" x="62"/>
-        <item h="1" x="52"/>
-        <item h="1" x="45"/>
-        <item h="1" x="61"/>
-        <item x="8"/>
-        <item h="1" x="40"/>
-        <item h="1" x="55"/>
-        <item h="1" x="19"/>
-        <item h="1" x="41"/>
-        <item h="1" x="50"/>
-        <item h="1" x="46"/>
-        <item h="1" x="43"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item h="1" x="11"/>
-        <item h="1" x="36"/>
-        <item h="1" x="70"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="47"/>
-        <item h="1" x="26"/>
-        <item h="1" x="68"/>
-        <item h="1" x="34"/>
-        <item h="1" x="12"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="69"/>
-        <item h="1" x="65"/>
-        <item h="1" x="53"/>
-        <item x="10"/>
-        <item h="1" x="58"/>
-        <item h="1" x="16"/>
-        <item h="1" x="59"/>
-        <item h="1" x="14"/>
-        <item x="6"/>
-        <item h="1" x="74"/>
-        <item h="1" x="57"/>
-        <item h="1" x="63"/>
-        <item h="1" x="20"/>
-        <item x="0"/>
-        <item h="1" x="60"/>
-        <item h="1" x="54"/>
-        <item h="1" x="5"/>
-        <item h="1" x="49"/>
-        <item x="17"/>
-        <item x="1"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="39"/>
-        <item h="1" x="25"/>
-        <item h="1" x="35"/>
-        <item h="1" x="71"/>
-        <item h="1" x="64"/>
-        <item h="1" x="44"/>
-        <item h="1" x="66"/>
-        <item h="1" x="18"/>
-        <item h="1" x="9"/>
-        <item x="3"/>
-        <item h="1" x="72"/>
-        <item h="1" x="29"/>
-        <item h="1" x="23"/>
-        <item h="1" x="13"/>
-        <item h="1" x="67"/>
-        <item h="1" x="48"/>
-        <item h="1" x="76"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="102">
-        <item x="60"/>
-        <item x="7"/>
-        <item x="91"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="5"/>
-        <item x="96"/>
-        <item x="25"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="77"/>
-        <item x="95"/>
-        <item x="83"/>
-        <item x="55"/>
-        <item x="22"/>
-        <item x="90"/>
-        <item x="94"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="63"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="61"/>
-        <item x="40"/>
-        <item x="15"/>
-        <item x="71"/>
-        <item x="99"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="59"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="58"/>
-        <item x="33"/>
-        <item x="46"/>
-        <item x="54"/>
-        <item x="3"/>
-        <item x="29"/>
-        <item x="93"/>
-        <item x="19"/>
-        <item x="24"/>
-        <item x="45"/>
-        <item x="26"/>
-        <item x="84"/>
-        <item x="36"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="87"/>
-        <item x="89"/>
-        <item x="17"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="32"/>
-        <item x="72"/>
-        <item x="8"/>
-        <item x="28"/>
-        <item x="57"/>
-        <item x="21"/>
-        <item x="88"/>
-        <item x="65"/>
-        <item x="80"/>
-        <item x="48"/>
-        <item x="97"/>
-        <item x="92"/>
-        <item x="30"/>
-        <item x="66"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="50"/>
-        <item x="35"/>
-        <item x="79"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="67"/>
-        <item x="74"/>
-        <item x="98"/>
-        <item x="44"/>
-        <item x="39"/>
-        <item x="78"/>
-        <item x="70"/>
-        <item x="76"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="82"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="75"/>
-        <item x="2"/>
-        <item x="27"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="102">
-        <item x="99"/>
-        <item x="98"/>
-        <item x="95"/>
-        <item x="97"/>
-        <item x="96"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="92"/>
-        <item x="91"/>
-        <item x="90"/>
-        <item x="89"/>
-        <item x="88"/>
-        <item x="87"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="71"/>
-        <item x="86"/>
-        <item x="78"/>
-        <item x="82"/>
-        <item x="76"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="60"/>
-        <item x="79"/>
-        <item x="77"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="52"/>
-        <item x="69"/>
-        <item x="72"/>
-        <item x="70"/>
-        <item x="68"/>
-        <item x="59"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="48"/>
-        <item x="67"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="61"/>
-        <item x="55"/>
-        <item x="54"/>
-        <item x="42"/>
-        <item x="75"/>
-        <item x="56"/>
-        <item x="39"/>
-        <item x="37"/>
-        <item x="58"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="47"/>
-        <item x="31"/>
-        <item x="63"/>
-        <item x="45"/>
-        <item x="30"/>
-        <item x="29"/>
-        <item x="27"/>
-        <item x="40"/>
-        <item x="20"/>
-        <item x="41"/>
-        <item x="57"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="33"/>
-        <item x="53"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="43"/>
-        <item x="18"/>
-        <item x="21"/>
-        <item x="44"/>
-        <item x="17"/>
-        <item x="51"/>
-        <item x="16"/>
-        <item x="38"/>
-        <item x="46"/>
-        <item x="13"/>
-        <item x="25"/>
-        <item x="34"/>
-        <item x="23"/>
-        <item x="11"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="26"/>
-        <item x="24"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Profit" fld="14" baseField="1" baseItem="16" numFmtId="166"/>
-    <dataField name="Revenue" fld="12" baseField="1" baseItem="16"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="10">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="41" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="42" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="48" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="50" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="51" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="50" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="48" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="51" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="56" rowHeaderCaption="Item Type">
-  <location ref="A17:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="14">
-        <item x="3"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item h="1" x="12"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
@@ -17679,1784 +16953,25 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="2"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="12">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
+  <rowItems count="1">
     <i>
       <x v="6"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="7"/>
     </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="9" baseField="2" baseItem="0" numFmtId="167"/>
+    <dataField name="Sum of Units Sold" fld="9" baseField="0" baseItem="6" numFmtId="167"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="12">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-  </formats>
-  <chartFormats count="130">
-    <chartFormat chart="24" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="17">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="18">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="19">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="20">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="21">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="22">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="23">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="24">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="25">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="26" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="27">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="28">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="29">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="30">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="31">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="32">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="33">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="34">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="35">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="36">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="37">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="38">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="39" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="40">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="41">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="42">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="43">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="44">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="45">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="46">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="47">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="48">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="49">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="50">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="51">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="52" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="53">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="54">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="55">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="56">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="57">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="58">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="59">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="60">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="61">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="62">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="63">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="64">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="65" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="66">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="67">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="68">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="69">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="70">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="71">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="72">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="73">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="74">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="75">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="76">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="77">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="78" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="79">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="80">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="81">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="82">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="83">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="84">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="85">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="86">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="87">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="88">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="89">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="35" format="90">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="78" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="79">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="80">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="81">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="82">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="83">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="84">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="85">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="86">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="87">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="88">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="89">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="36" format="90">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="78" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="79">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="80">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="81">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="82">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="83">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="84">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="85">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="86">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="87">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="88">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="89">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="90">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="91" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="92">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="93">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="94">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="95">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="96">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="97">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="98">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="99">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="100">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="101">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="102">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="103">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Item Type">
-  <location ref="D33:E34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="14">
-        <item x="3"/>
-        <item h="1" x="10"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item h="1" x="0"/>
-        <item h="1" x="11"/>
-        <item h="1" x="1"/>
-        <item h="1" x="8"/>
-        <item h="1" x="2"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item h="1" x="6"/>
-        <item h="1" x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="102">
-        <item x="60"/>
-        <item x="7"/>
-        <item x="91"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="37"/>
-        <item x="5"/>
-        <item x="96"/>
-        <item x="25"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="77"/>
-        <item x="95"/>
-        <item x="83"/>
-        <item x="55"/>
-        <item x="22"/>
-        <item x="90"/>
-        <item x="94"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="63"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="61"/>
-        <item x="40"/>
-        <item x="15"/>
-        <item x="71"/>
-        <item x="99"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="59"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="58"/>
-        <item x="33"/>
-        <item x="46"/>
-        <item x="54"/>
-        <item x="3"/>
-        <item x="29"/>
-        <item x="93"/>
-        <item x="19"/>
-        <item x="24"/>
-        <item x="45"/>
-        <item x="26"/>
-        <item x="84"/>
-        <item x="36"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="87"/>
-        <item x="89"/>
-        <item x="17"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="32"/>
-        <item x="72"/>
-        <item x="8"/>
-        <item x="28"/>
-        <item x="57"/>
-        <item x="21"/>
-        <item x="88"/>
-        <item x="65"/>
-        <item x="80"/>
-        <item x="48"/>
-        <item x="97"/>
-        <item x="92"/>
-        <item x="30"/>
-        <item x="66"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="50"/>
-        <item x="35"/>
-        <item x="79"/>
-        <item x="31"/>
-        <item x="64"/>
-        <item x="67"/>
-        <item x="74"/>
-        <item x="98"/>
-        <item x="44"/>
-        <item x="39"/>
-        <item x="78"/>
-        <item x="70"/>
-        <item x="76"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="82"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="75"/>
-        <item x="2"/>
-        <item x="27"/>
-        <item x="51"/>
-        <item x="4"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="1">
-    <i>
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Profit" fld="14" baseField="2" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="14">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -19468,7 +16983,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
   <location ref="H12:H13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
@@ -20043,10 +17558,10 @@
     <dataField name="Sum of Units Sold" fld="9" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="16">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -20059,25 +17574,1802 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Region">
-  <location ref="D28:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="56" rowHeaderCaption="Item Type">
+  <location ref="A17:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="9">
-        <item h="1" x="4"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="0"/>
-        <item h="1" x="6"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
         <item x="5"/>
         <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="14">
+        <item x="3"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item h="1" x="12"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="102">
+        <item x="60"/>
+        <item x="7"/>
+        <item x="91"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="96"/>
+        <item x="25"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="77"/>
+        <item x="95"/>
+        <item x="83"/>
+        <item x="55"/>
+        <item x="22"/>
+        <item x="90"/>
+        <item x="94"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="63"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="61"/>
+        <item x="40"/>
+        <item x="15"/>
+        <item x="71"/>
+        <item x="99"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="58"/>
+        <item x="33"/>
+        <item x="46"/>
+        <item x="54"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="93"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="45"/>
+        <item x="26"/>
+        <item x="84"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="87"/>
+        <item x="89"/>
+        <item x="17"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="32"/>
+        <item x="72"/>
+        <item x="8"/>
+        <item x="28"/>
+        <item x="57"/>
+        <item x="21"/>
+        <item x="88"/>
+        <item x="65"/>
+        <item x="80"/>
+        <item x="48"/>
+        <item x="97"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="66"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="50"/>
+        <item x="35"/>
+        <item x="79"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="67"/>
+        <item x="74"/>
+        <item x="98"/>
+        <item x="44"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="70"/>
+        <item x="76"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="82"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="75"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="9" baseField="2" baseItem="0" numFmtId="167"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="130">
+    <chartFormat chart="24" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="17">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="18">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="19">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="20">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="21">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="22">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="23">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="24">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="25">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="27">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="28">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="29">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="30">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="31">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="32">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="33">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="34">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="35">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="36">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="37">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="38">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="39" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="40">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="41">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="42">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="43">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="44">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="45">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="46">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="47">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="48">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="49">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="50">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="51">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="52" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="53">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="54">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="55">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="56">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="57">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="58">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="59">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="60">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="61">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="62">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="63">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="64">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="65" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="66">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="67">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="68">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="69">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="70">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="71">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="72">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="73">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="74">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="75">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="76">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="77">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="78" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="79">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="80">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="81">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="82">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="83">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="84">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="85">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="86">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="87">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="88">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="89">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="90">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="78" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="79">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="80">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="81">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="82">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="83">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="84">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="85">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="86">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="87">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="88">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="89">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="36" format="90">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="78" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="79">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="80">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="81">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="82">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="83">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="84">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="85">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="86">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="87">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="88">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="89">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="90">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="91" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="92">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="93">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="94">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="95">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="96">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="97">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="98">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="99">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="100">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="101">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="102">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="103">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
+  <location ref="A33:B40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="9">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
@@ -20201,14 +19493,32 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="1">
+  <rowItems count="7">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
     <i>
       <x v="6"/>
     </i>
@@ -20217,14 +19527,77 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Item Type" fld="2" subtotal="count" baseField="0" baseItem="0" numFmtId="1"/>
+    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="18">
+  <formats count="9">
+    <format dxfId="31">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="17">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -20236,9 +19609,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54" rowHeaderCaption="Sales Channel">
-  <location ref="K19:K20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="88" rowHeaderCaption="Country">
+  <location ref="A3:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0">
       <items count="9">
@@ -20253,16 +19626,99 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="78">
+        <item h="1" x="51"/>
+        <item h="1" x="22"/>
+        <item h="1" x="38"/>
+        <item h="1" x="32"/>
+        <item x="7"/>
+        <item h="1" x="24"/>
+        <item h="1" x="37"/>
+        <item h="1" x="15"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="21"/>
+        <item h="1" x="42"/>
+        <item h="1" x="62"/>
+        <item h="1" x="52"/>
+        <item h="1" x="45"/>
+        <item h="1" x="61"/>
+        <item x="8"/>
+        <item h="1" x="40"/>
+        <item h="1" x="55"/>
+        <item h="1" x="19"/>
+        <item h="1" x="41"/>
+        <item h="1" x="50"/>
+        <item h="1" x="46"/>
+        <item h="1" x="43"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item h="1" x="11"/>
+        <item h="1" x="36"/>
+        <item h="1" x="70"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="47"/>
+        <item h="1" x="26"/>
+        <item h="1" x="68"/>
+        <item h="1" x="34"/>
+        <item h="1" x="12"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="69"/>
+        <item h="1" x="65"/>
+        <item h="1" x="53"/>
+        <item x="10"/>
+        <item h="1" x="58"/>
+        <item h="1" x="16"/>
+        <item h="1" x="59"/>
+        <item h="1" x="14"/>
+        <item x="6"/>
+        <item h="1" x="74"/>
+        <item h="1" x="57"/>
+        <item h="1" x="63"/>
+        <item h="1" x="20"/>
+        <item x="0"/>
+        <item h="1" x="60"/>
+        <item h="1" x="54"/>
+        <item h="1" x="5"/>
+        <item h="1" x="49"/>
+        <item x="17"/>
+        <item x="1"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="39"/>
+        <item h="1" x="25"/>
+        <item h="1" x="35"/>
+        <item h="1" x="71"/>
+        <item h="1" x="64"/>
+        <item h="1" x="44"/>
+        <item h="1" x="66"/>
+        <item h="1" x="18"/>
+        <item h="1" x="9"/>
+        <item x="3"/>
+        <item h="1" x="72"/>
+        <item h="1" x="29"/>
+        <item h="1" x="23"/>
+        <item h="1" x="13"/>
+        <item h="1" x="67"/>
+        <item h="1" x="48"/>
+        <item h="1" x="76"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0">
       <items count="6">
         <item x="2"/>
@@ -20379,118 +19835,510 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="102">
-        <item x="52"/>
-        <item x="24"/>
-        <item x="56"/>
-        <item x="23"/>
-        <item x="97"/>
-        <item x="44"/>
-        <item x="94"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="68"/>
-        <item x="27"/>
-        <item x="34"/>
-        <item x="19"/>
-        <item x="66"/>
-        <item x="39"/>
-        <item x="58"/>
-        <item x="0"/>
-        <item x="65"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="46"/>
-        <item x="2"/>
-        <item x="57"/>
-        <item x="82"/>
-        <item x="92"/>
-        <item x="7"/>
-        <item x="60"/>
-        <item x="85"/>
-        <item x="9"/>
-        <item x="53"/>
-        <item x="61"/>
-        <item x="80"/>
-        <item x="25"/>
-        <item x="38"/>
-        <item x="84"/>
-        <item x="62"/>
-        <item x="26"/>
-        <item x="32"/>
-        <item x="49"/>
-        <item x="89"/>
-        <item x="83"/>
-        <item x="99"/>
-        <item x="88"/>
-        <item x="79"/>
-        <item x="4"/>
-        <item x="50"/>
-        <item x="18"/>
-        <item x="67"/>
-        <item x="36"/>
-        <item x="77"/>
-        <item x="31"/>
-        <item x="28"/>
-        <item x="96"/>
-        <item x="75"/>
-        <item x="20"/>
-        <item x="5"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="1"/>
-        <item x="91"/>
-        <item x="16"/>
-        <item x="81"/>
-        <item x="17"/>
-        <item x="37"/>
-        <item x="76"/>
-        <item x="70"/>
-        <item x="41"/>
-        <item x="93"/>
-        <item x="64"/>
-        <item x="30"/>
-        <item x="55"/>
-        <item x="73"/>
-        <item x="42"/>
-        <item x="90"/>
-        <item x="95"/>
-        <item x="98"/>
-        <item x="21"/>
-        <item x="51"/>
-        <item x="40"/>
-        <item x="72"/>
-        <item x="63"/>
-        <item x="45"/>
-        <item x="74"/>
-        <item x="35"/>
-        <item x="33"/>
-        <item x="43"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="87"/>
-        <item x="48"/>
-        <item x="86"/>
-        <item x="69"/>
-        <item x="54"/>
-        <item x="71"/>
-        <item x="10"/>
-        <item x="59"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="102">
+        <item x="99"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="97"/>
+        <item x="96"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="92"/>
+        <item x="91"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="88"/>
+        <item x="87"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="71"/>
+        <item x="86"/>
+        <item x="78"/>
+        <item x="82"/>
+        <item x="76"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="60"/>
+        <item x="79"/>
+        <item x="77"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="52"/>
+        <item x="69"/>
+        <item x="72"/>
+        <item x="70"/>
+        <item x="68"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="48"/>
+        <item x="67"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="61"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="42"/>
+        <item x="75"/>
+        <item x="56"/>
+        <item x="39"/>
+        <item x="37"/>
+        <item x="58"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="47"/>
+        <item x="31"/>
+        <item x="63"/>
+        <item x="45"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="20"/>
+        <item x="41"/>
+        <item x="57"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="33"/>
+        <item x="53"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="43"/>
+        <item x="18"/>
+        <item x="21"/>
+        <item x="44"/>
+        <item x="17"/>
+        <item x="51"/>
+        <item x="16"/>
+        <item x="38"/>
+        <item x="46"/>
+        <item x="13"/>
+        <item x="25"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Profit" fld="14" baseField="1" baseItem="16" numFmtId="166"/>
+    <dataField name="Revenue" fld="12" baseField="1" baseItem="16"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="41" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="42" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="48" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="50" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="51" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="50" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="48" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="51" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
+  <location ref="H3:H4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="15">
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="102">
+        <item x="60"/>
+        <item x="7"/>
+        <item x="91"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="96"/>
+        <item x="25"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="77"/>
+        <item x="95"/>
+        <item x="83"/>
+        <item x="55"/>
+        <item x="22"/>
+        <item x="90"/>
+        <item x="94"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="63"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="61"/>
+        <item x="40"/>
+        <item x="15"/>
+        <item x="71"/>
+        <item x="99"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="58"/>
+        <item x="33"/>
+        <item x="46"/>
+        <item x="54"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="93"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="45"/>
+        <item x="26"/>
+        <item x="84"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="87"/>
+        <item x="89"/>
+        <item x="17"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="32"/>
+        <item x="72"/>
+        <item x="8"/>
+        <item x="28"/>
+        <item x="57"/>
+        <item x="21"/>
+        <item x="88"/>
+        <item x="65"/>
+        <item x="80"/>
+        <item x="48"/>
+        <item x="97"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="66"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="50"/>
+        <item x="35"/>
+        <item x="79"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="67"/>
+        <item x="74"/>
+        <item x="98"/>
+        <item x="44"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="70"/>
+        <item x="76"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="82"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="75"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="102">
+        <item x="99"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="97"/>
+        <item x="96"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="92"/>
+        <item x="91"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="88"/>
+        <item x="87"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="71"/>
+        <item x="86"/>
+        <item x="78"/>
+        <item x="82"/>
+        <item x="76"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="60"/>
+        <item x="79"/>
+        <item x="77"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="52"/>
+        <item x="69"/>
+        <item x="72"/>
+        <item x="70"/>
+        <item x="68"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="48"/>
+        <item x="67"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="61"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="42"/>
+        <item x="75"/>
+        <item x="56"/>
+        <item x="39"/>
+        <item x="37"/>
+        <item x="58"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="47"/>
+        <item x="31"/>
+        <item x="63"/>
+        <item x="45"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="20"/>
+        <item x="41"/>
+        <item x="57"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="33"/>
+        <item x="53"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="43"/>
+        <item x="18"/>
+        <item x="21"/>
+        <item x="44"/>
+        <item x="17"/>
+        <item x="51"/>
+        <item x="16"/>
+        <item x="38"/>
+        <item x="46"/>
+        <item x="13"/>
+        <item x="25"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -20501,8 +20349,372 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Order ID" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="35">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Region">
+  <location ref="E3:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="102">
+        <item x="60"/>
+        <item x="7"/>
+        <item x="91"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="96"/>
+        <item x="25"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="56"/>
+        <item x="23"/>
+        <item x="77"/>
+        <item x="95"/>
+        <item x="83"/>
+        <item x="55"/>
+        <item x="22"/>
+        <item x="90"/>
+        <item x="94"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="63"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="61"/>
+        <item x="40"/>
+        <item x="15"/>
+        <item x="71"/>
+        <item x="99"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="58"/>
+        <item x="33"/>
+        <item x="46"/>
+        <item x="54"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="93"/>
+        <item x="19"/>
+        <item x="24"/>
+        <item x="45"/>
+        <item x="26"/>
+        <item x="84"/>
+        <item x="36"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="87"/>
+        <item x="89"/>
+        <item x="17"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="32"/>
+        <item x="72"/>
+        <item x="8"/>
+        <item x="28"/>
+        <item x="57"/>
+        <item x="21"/>
+        <item x="88"/>
+        <item x="65"/>
+        <item x="80"/>
+        <item x="48"/>
+        <item x="97"/>
+        <item x="92"/>
+        <item x="30"/>
+        <item x="66"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="50"/>
+        <item x="35"/>
+        <item x="79"/>
+        <item x="31"/>
+        <item x="64"/>
+        <item x="67"/>
+        <item x="74"/>
+        <item x="98"/>
+        <item x="44"/>
+        <item x="39"/>
+        <item x="78"/>
+        <item x="70"/>
+        <item x="76"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="82"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="75"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="51"/>
+        <item x="4"/>
+        <item x="41"/>
+        <item x="81"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="100"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Revenue" fld="12" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="44">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="42">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="39">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="38">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="32" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -20513,8 +20725,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
-  <location ref="H9:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Priority">
+  <location ref="H6:H7" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField showAll="0">
       <items count="9">
@@ -20760,7 +20972,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField dataField="1" showAll="0">
       <items count="102">
         <item x="99"/>
         <item x="98"/>
@@ -20866,112 +21078,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="102">
-        <item x="99"/>
-        <item x="98"/>
-        <item x="97"/>
-        <item x="96"/>
-        <item x="95"/>
-        <item x="94"/>
-        <item x="93"/>
-        <item x="92"/>
-        <item x="91"/>
-        <item x="90"/>
-        <item x="89"/>
-        <item x="88"/>
-        <item x="87"/>
-        <item x="86"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="83"/>
-        <item x="82"/>
-        <item x="81"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="78"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="75"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="72"/>
-        <item x="71"/>
-        <item x="70"/>
-        <item x="69"/>
-        <item x="68"/>
-        <item x="67"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="64"/>
-        <item x="63"/>
-        <item x="62"/>
-        <item x="61"/>
-        <item x="60"/>
-        <item x="59"/>
-        <item x="58"/>
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="54"/>
-        <item x="53"/>
-        <item x="52"/>
-        <item x="51"/>
-        <item x="50"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="45"/>
-        <item x="44"/>
-        <item x="43"/>
-        <item x="42"/>
-        <item x="41"/>
-        <item x="40"/>
-        <item x="39"/>
-        <item x="38"/>
-        <item x="37"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="25"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="100"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -20980,13 +21087,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Profit" fld="14" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Cost" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="20">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -21512,7 +21619,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>7</v>
@@ -26362,14 +26469,14 @@
     <col min="1" max="1" width="32.42578125" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" style="10" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" customWidth="1"/>
     <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="27" width="10" customWidth="1"/>
     <col min="28" max="70" width="10" bestFit="1" customWidth="1"/>
@@ -26382,10 +26489,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>0</v>
@@ -26397,10 +26504,10 @@
         <v>116</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -26426,8 +26533,8 @@
         <f>GETPIVOTDATA("Total Revenue",$H$3)</f>
         <v>137348768.30999991</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>52</v>
+      <c r="K4" s="5">
+        <v>585920464</v>
       </c>
       <c r="L4" s="6">
         <v>50</v>
@@ -26628,7 +26735,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>2</v>
@@ -26677,7 +26784,7 @@
         <v>888047.28</v>
       </c>
       <c r="K19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -26822,7 +26929,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>58</v>
@@ -26841,8 +26948,8 @@
       <c r="D29" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="9">
-        <v>36</v>
+      <c r="E29" s="18">
+        <v>182870</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>37</v>
